--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -6550,10 +6550,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119716230</v>
+        <v>119716909</v>
       </c>
       <c r="B58" t="n">
-        <v>8421</v>
+        <v>105009</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6566,39 +6566,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674120</v>
+        <v>674221</v>
       </c>
       <c r="R58" t="n">
-        <v>6607622</v>
+        <v>6607862</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6657,7 +6652,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119716909</v>
+        <v>119715944</v>
       </c>
       <c r="B59" t="n">
         <v>105009</v>
@@ -6697,10 +6692,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674221</v>
+        <v>674171</v>
       </c>
       <c r="R59" t="n">
-        <v>6607862</v>
+        <v>6607629</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6759,10 +6754,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119715944</v>
+        <v>119716230</v>
       </c>
       <c r="B60" t="n">
-        <v>105009</v>
+        <v>8421</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6775,34 +6770,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674171</v>
+        <v>674120</v>
       </c>
       <c r="R60" t="n">
-        <v>6607629</v>
+        <v>6607622</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -4447,7 +4447,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119716905</v>
+        <v>119719516</v>
       </c>
       <c r="B38" t="n">
         <v>57326</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674225</v>
+        <v>674419</v>
       </c>
       <c r="R38" t="n">
-        <v>6607864</v>
+        <v>6607656</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119717648</v>
+        <v>119717489</v>
       </c>
       <c r="B39" t="n">
-        <v>5169</v>
+        <v>100171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,29 +4570,24 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
@@ -4602,7 +4597,7 @@
         <v>674162</v>
       </c>
       <c r="R39" t="n">
-        <v>6607842</v>
+        <v>6607837</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4661,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119719393</v>
+        <v>119718022</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>104994</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4673,43 +4668,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674375</v>
+        <v>674216</v>
       </c>
       <c r="R40" t="n">
-        <v>6607681</v>
+        <v>6607800</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,10 +4772,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119717604</v>
+        <v>119717672</v>
       </c>
       <c r="B41" t="n">
-        <v>100171</v>
+        <v>91182</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,21 +4788,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4808,10 +4812,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674141</v>
+        <v>674166</v>
       </c>
       <c r="R41" t="n">
-        <v>6607853</v>
+        <v>6607847</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4874,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119717226</v>
+        <v>119719393</v>
       </c>
       <c r="B42" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,42 +4890,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674169</v>
+        <v>674375</v>
       </c>
       <c r="R42" t="n">
-        <v>6607879</v>
+        <v>6607681</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4977,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119717414</v>
+        <v>119717027</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4989,52 +4993,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674201</v>
+        <v>674194</v>
       </c>
       <c r="R43" t="n">
-        <v>6607851</v>
+        <v>6607917</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,11 +5057,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5098,10 +5083,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119717672</v>
+        <v>119714171</v>
       </c>
       <c r="B44" t="n">
-        <v>91182</v>
+        <v>100171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5114,34 +5099,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674166</v>
+        <v>674356</v>
       </c>
       <c r="R44" t="n">
-        <v>6607847</v>
+        <v>6607520</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5200,10 +5185,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119718457</v>
+        <v>119716230</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>8421</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5212,38 +5197,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674202</v>
+        <v>674120</v>
       </c>
       <c r="R45" t="n">
-        <v>6607652</v>
+        <v>6607622</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5302,10 +5292,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119718022</v>
+        <v>119716495</v>
       </c>
       <c r="B46" t="n">
-        <v>104994</v>
+        <v>105009</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5318,48 +5308,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221725</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674216</v>
+        <v>674218</v>
       </c>
       <c r="R46" t="n">
-        <v>6607800</v>
+        <v>6607746</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,10 +5394,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119716052</v>
+        <v>119719729</v>
       </c>
       <c r="B47" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5434,34 +5410,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674152</v>
+        <v>674432</v>
       </c>
       <c r="R47" t="n">
-        <v>6607643</v>
+        <v>6607590</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,10 +5496,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119718472</v>
+        <v>119716905</v>
       </c>
       <c r="B48" t="n">
-        <v>105009</v>
+        <v>57326</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5532,38 +5508,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674198</v>
+        <v>674225</v>
       </c>
       <c r="R48" t="n">
-        <v>6607655</v>
+        <v>6607864</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,7 +5603,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119714171</v>
+        <v>119717688</v>
       </c>
       <c r="B49" t="n">
         <v>100171</v>
@@ -5658,14 +5639,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674356</v>
+        <v>674174</v>
       </c>
       <c r="R49" t="n">
-        <v>6607520</v>
+        <v>6607837</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5724,10 +5705,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119716838</v>
+        <v>119718622</v>
       </c>
       <c r="B50" t="n">
-        <v>100171</v>
+        <v>105009</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5740,34 +5721,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674257</v>
+        <v>674249</v>
       </c>
       <c r="R50" t="n">
-        <v>6607850</v>
+        <v>6607621</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5826,10 +5807,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119717027</v>
+        <v>119717604</v>
       </c>
       <c r="B51" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5842,21 +5823,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5866,10 +5847,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674194</v>
+        <v>674141</v>
       </c>
       <c r="R51" t="n">
-        <v>6607917</v>
+        <v>6607853</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5928,10 +5909,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119716973</v>
+        <v>119717648</v>
       </c>
       <c r="B52" t="n">
-        <v>57326</v>
+        <v>5169</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5940,31 +5921,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5973,10 +5954,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674194</v>
+        <v>674162</v>
       </c>
       <c r="R52" t="n">
-        <v>6607881</v>
+        <v>6607842</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6035,10 +6016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119719516</v>
+        <v>119717226</v>
       </c>
       <c r="B53" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6051,42 +6032,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674419</v>
+        <v>674169</v>
       </c>
       <c r="R53" t="n">
-        <v>6607656</v>
+        <v>6607879</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6142,7 +6123,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119718622</v>
+        <v>119716909</v>
       </c>
       <c r="B54" t="n">
         <v>105009</v>
@@ -6178,14 +6159,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674249</v>
+        <v>674221</v>
       </c>
       <c r="R54" t="n">
-        <v>6607621</v>
+        <v>6607862</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6244,10 +6225,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119717195</v>
+        <v>119715944</v>
       </c>
       <c r="B55" t="n">
-        <v>74577</v>
+        <v>105009</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6260,21 +6241,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6284,10 +6265,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674160</v>
+        <v>674171</v>
       </c>
       <c r="R55" t="n">
-        <v>6607881</v>
+        <v>6607629</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6346,10 +6327,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119715881</v>
+        <v>119716838</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>100171</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6358,25 +6339,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6386,13 +6367,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674166</v>
+        <v>674257</v>
       </c>
       <c r="R56" t="n">
-        <v>6607637</v>
+        <v>6607850</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6448,10 +6429,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119717489</v>
+        <v>119714906</v>
       </c>
       <c r="B57" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6460,38 +6441,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674162</v>
+        <v>674311</v>
       </c>
       <c r="R57" t="n">
-        <v>6607837</v>
+        <v>6607664</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6550,10 +6531,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119716909</v>
+        <v>119717195</v>
       </c>
       <c r="B58" t="n">
-        <v>105009</v>
+        <v>74577</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6566,21 +6547,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6590,10 +6571,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674221</v>
+        <v>674160</v>
       </c>
       <c r="R58" t="n">
-        <v>6607862</v>
+        <v>6607881</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6652,7 +6633,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119715944</v>
+        <v>119718472</v>
       </c>
       <c r="B59" t="n">
         <v>105009</v>
@@ -6692,10 +6673,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674171</v>
+        <v>674198</v>
       </c>
       <c r="R59" t="n">
-        <v>6607629</v>
+        <v>6607655</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6754,10 +6735,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119716230</v>
+        <v>119717901</v>
       </c>
       <c r="B60" t="n">
-        <v>8421</v>
+        <v>57326</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6766,31 +6747,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6799,10 +6780,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674120</v>
+        <v>674244</v>
       </c>
       <c r="R60" t="n">
-        <v>6607622</v>
+        <v>6607812</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6861,10 +6842,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119716495</v>
+        <v>119716973</v>
       </c>
       <c r="B61" t="n">
-        <v>105009</v>
+        <v>57326</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6873,38 +6854,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674218</v>
+        <v>674194</v>
       </c>
       <c r="R61" t="n">
-        <v>6607746</v>
+        <v>6607881</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6963,10 +6949,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119719729</v>
+        <v>119717414</v>
       </c>
       <c r="B62" t="n">
-        <v>100171</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6975,38 +6961,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674432</v>
+        <v>674201</v>
       </c>
       <c r="R62" t="n">
-        <v>6607590</v>
+        <v>6607851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7039,6 +7039,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7065,10 +7070,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119717688</v>
+        <v>119715881</v>
       </c>
       <c r="B63" t="n">
-        <v>100171</v>
+        <v>57463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7077,25 +7082,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7105,13 +7110,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674174</v>
+        <v>674166</v>
       </c>
       <c r="R63" t="n">
-        <v>6607837</v>
+        <v>6607637</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7167,10 +7172,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119714906</v>
+        <v>119718457</v>
       </c>
       <c r="B64" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7183,34 +7188,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674311</v>
+        <v>674202</v>
       </c>
       <c r="R64" t="n">
-        <v>6607664</v>
+        <v>6607652</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7269,10 +7274,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119717901</v>
+        <v>119716052</v>
       </c>
       <c r="B65" t="n">
-        <v>57326</v>
+        <v>105009</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7281,43 +7286,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674244</v>
+        <v>674152</v>
       </c>
       <c r="R65" t="n">
-        <v>6607812</v>
+        <v>6607643</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119719516</v>
+        <v>119717672</v>
       </c>
       <c r="B38" t="n">
-        <v>57326</v>
+        <v>91182</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,43 +4459,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674419</v>
+        <v>674166</v>
       </c>
       <c r="R38" t="n">
-        <v>6607656</v>
+        <v>6607847</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119717489</v>
+        <v>119719516</v>
       </c>
       <c r="B39" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4566,38 +4561,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674162</v>
+        <v>674419</v>
       </c>
       <c r="R39" t="n">
-        <v>6607837</v>
+        <v>6607656</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119717672</v>
+        <v>119717489</v>
       </c>
       <c r="B41" t="n">
-        <v>91182</v>
+        <v>100171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4788,21 +4788,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674166</v>
+        <v>674162</v>
       </c>
       <c r="R41" t="n">
-        <v>6607847</v>
+        <v>6607837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6842,10 +6842,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119716973</v>
+        <v>119717414</v>
       </c>
       <c r="B61" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6854,31 +6854,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6887,10 +6896,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674194</v>
+        <v>674201</v>
       </c>
       <c r="R61" t="n">
-        <v>6607881</v>
+        <v>6607851</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6923,6 +6932,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6949,10 +6963,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119717414</v>
+        <v>119716973</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6961,40 +6975,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7003,10 +7008,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674201</v>
+        <v>674194</v>
       </c>
       <c r="R62" t="n">
-        <v>6607851</v>
+        <v>6607881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7039,11 +7044,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119717672</v>
+        <v>119717226</v>
       </c>
       <c r="B38" t="n">
-        <v>91182</v>
+        <v>57463</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,41 +4459,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674166</v>
+        <v>674169</v>
       </c>
       <c r="R38" t="n">
-        <v>6607847</v>
+        <v>6607879</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4549,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119719516</v>
+        <v>119716838</v>
       </c>
       <c r="B39" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4561,43 +4566,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674419</v>
+        <v>674257</v>
       </c>
       <c r="R39" t="n">
-        <v>6607656</v>
+        <v>6607850</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119718022</v>
+        <v>119715881</v>
       </c>
       <c r="B40" t="n">
-        <v>104994</v>
+        <v>57463</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,55 +4668,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674216</v>
+        <v>674166</v>
       </c>
       <c r="R40" t="n">
-        <v>6607800</v>
+        <v>6607637</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4772,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119717489</v>
+        <v>119717195</v>
       </c>
       <c r="B41" t="n">
-        <v>100171</v>
+        <v>74577</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4788,21 +4774,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4812,10 +4798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674162</v>
+        <v>674160</v>
       </c>
       <c r="R41" t="n">
-        <v>6607837</v>
+        <v>6607881</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,10 +4860,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119719393</v>
+        <v>119716495</v>
       </c>
       <c r="B42" t="n">
-        <v>57326</v>
+        <v>105009</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,43 +4872,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674375</v>
+        <v>674218</v>
       </c>
       <c r="R42" t="n">
-        <v>6607681</v>
+        <v>6607746</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4981,10 +4962,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119717027</v>
+        <v>119717672</v>
       </c>
       <c r="B43" t="n">
-        <v>105009</v>
+        <v>91182</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4997,21 +4978,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5021,10 +5002,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674194</v>
+        <v>674166</v>
       </c>
       <c r="R43" t="n">
-        <v>6607917</v>
+        <v>6607847</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5083,10 +5064,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119714171</v>
+        <v>119719393</v>
       </c>
       <c r="B44" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5095,38 +5076,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674356</v>
+        <v>674375</v>
       </c>
       <c r="R44" t="n">
-        <v>6607520</v>
+        <v>6607681</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5185,10 +5171,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119716230</v>
+        <v>119716905</v>
       </c>
       <c r="B45" t="n">
-        <v>8421</v>
+        <v>57326</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5197,31 +5183,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5230,10 +5216,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674120</v>
+        <v>674225</v>
       </c>
       <c r="R45" t="n">
-        <v>6607622</v>
+        <v>6607864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5292,10 +5278,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119716495</v>
+        <v>119717489</v>
       </c>
       <c r="B46" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5308,21 +5294,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5332,10 +5318,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674218</v>
+        <v>674162</v>
       </c>
       <c r="R46" t="n">
-        <v>6607746</v>
+        <v>6607837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,10 +5482,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119716905</v>
+        <v>119717604</v>
       </c>
       <c r="B48" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,43 +5494,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674225</v>
+        <v>674141</v>
       </c>
       <c r="R48" t="n">
-        <v>6607864</v>
+        <v>6607853</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5603,10 +5584,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119717688</v>
+        <v>119716973</v>
       </c>
       <c r="B49" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,38 +5596,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674174</v>
+        <v>674194</v>
       </c>
       <c r="R49" t="n">
-        <v>6607837</v>
+        <v>6607881</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5705,10 +5691,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119718622</v>
+        <v>119718022</v>
       </c>
       <c r="B50" t="n">
-        <v>105009</v>
+        <v>104994</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5721,34 +5707,48 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>221725</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674249</v>
+        <v>674216</v>
       </c>
       <c r="R50" t="n">
-        <v>6607621</v>
+        <v>6607800</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119717604</v>
+        <v>119718472</v>
       </c>
       <c r="B51" t="n">
-        <v>100171</v>
+        <v>105009</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674141</v>
+        <v>674198</v>
       </c>
       <c r="R51" t="n">
-        <v>6607853</v>
+        <v>6607655</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717648</v>
+        <v>119717027</v>
       </c>
       <c r="B52" t="n">
-        <v>5169</v>
+        <v>105009</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5925,39 +5925,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674162</v>
+        <v>674194</v>
       </c>
       <c r="R52" t="n">
-        <v>6607842</v>
+        <v>6607917</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6016,10 +6011,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119717226</v>
+        <v>119717414</v>
       </c>
       <c r="B53" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6028,31 +6023,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6061,13 +6065,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674169</v>
+        <v>674201</v>
       </c>
       <c r="R53" t="n">
-        <v>6607879</v>
+        <v>6607851</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6097,6 +6101,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6123,10 +6132,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119716909</v>
+        <v>119718457</v>
       </c>
       <c r="B54" t="n">
-        <v>105009</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6135,38 +6144,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674221</v>
+        <v>674202</v>
       </c>
       <c r="R54" t="n">
-        <v>6607862</v>
+        <v>6607652</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6225,10 +6234,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119715944</v>
+        <v>119714171</v>
       </c>
       <c r="B55" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6241,34 +6250,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674171</v>
+        <v>674356</v>
       </c>
       <c r="R55" t="n">
-        <v>6607629</v>
+        <v>6607520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6327,7 +6336,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119716838</v>
+        <v>119717688</v>
       </c>
       <c r="B56" t="n">
         <v>100171</v>
@@ -6367,10 +6376,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674257</v>
+        <v>674174</v>
       </c>
       <c r="R56" t="n">
-        <v>6607850</v>
+        <v>6607837</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6429,10 +6438,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119714906</v>
+        <v>119718622</v>
       </c>
       <c r="B57" t="n">
-        <v>95455</v>
+        <v>105009</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6441,38 +6450,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674311</v>
+        <v>674249</v>
       </c>
       <c r="R57" t="n">
-        <v>6607664</v>
+        <v>6607621</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6531,10 +6540,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119717195</v>
+        <v>119719516</v>
       </c>
       <c r="B58" t="n">
-        <v>74577</v>
+        <v>57326</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6543,38 +6552,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674160</v>
+        <v>674419</v>
       </c>
       <c r="R58" t="n">
-        <v>6607881</v>
+        <v>6607656</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6633,7 +6647,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119718472</v>
+        <v>119716052</v>
       </c>
       <c r="B59" t="n">
         <v>105009</v>
@@ -6673,10 +6687,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674198</v>
+        <v>674152</v>
       </c>
       <c r="R59" t="n">
-        <v>6607655</v>
+        <v>6607643</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6735,10 +6749,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119717901</v>
+        <v>119715944</v>
       </c>
       <c r="B60" t="n">
-        <v>57326</v>
+        <v>105009</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6747,43 +6761,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674244</v>
+        <v>674171</v>
       </c>
       <c r="R60" t="n">
-        <v>6607812</v>
+        <v>6607629</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6842,10 +6851,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119717414</v>
+        <v>119717901</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6854,40 +6863,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674201</v>
+        <v>674244</v>
       </c>
       <c r="R61" t="n">
-        <v>6607851</v>
+        <v>6607812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,11 +6932,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6963,10 +6958,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119716973</v>
+        <v>119717648</v>
       </c>
       <c r="B62" t="n">
-        <v>57326</v>
+        <v>5169</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6975,31 +6970,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7008,10 +7003,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674194</v>
+        <v>674162</v>
       </c>
       <c r="R62" t="n">
-        <v>6607881</v>
+        <v>6607842</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7070,10 +7065,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119715881</v>
+        <v>119714906</v>
       </c>
       <c r="B63" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7086,37 +7081,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674166</v>
+        <v>674311</v>
       </c>
       <c r="R63" t="n">
-        <v>6607637</v>
+        <v>6607664</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7172,10 +7167,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119718457</v>
+        <v>119716230</v>
       </c>
       <c r="B64" t="n">
-        <v>90562</v>
+        <v>8421</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7184,38 +7179,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674202</v>
+        <v>674120</v>
       </c>
       <c r="R64" t="n">
-        <v>6607652</v>
+        <v>6607622</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7274,7 +7274,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119716052</v>
+        <v>119716909</v>
       </c>
       <c r="B65" t="n">
         <v>105009</v>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674152</v>
+        <v>674221</v>
       </c>
       <c r="R65" t="n">
-        <v>6607643</v>
+        <v>6607862</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -4656,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119715881</v>
+        <v>119717195</v>
       </c>
       <c r="B40" t="n">
-        <v>57463</v>
+        <v>74577</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,25 +4668,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4696,13 +4696,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674166</v>
+        <v>674160</v>
       </c>
       <c r="R40" t="n">
-        <v>6607637</v>
+        <v>6607881</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119717195</v>
+        <v>119715881</v>
       </c>
       <c r="B41" t="n">
-        <v>74577</v>
+        <v>57463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4770,25 +4770,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674160</v>
+        <v>674166</v>
       </c>
       <c r="R41" t="n">
-        <v>6607881</v>
+        <v>6607637</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119716052</v>
+        <v>119717648</v>
       </c>
       <c r="B59" t="n">
-        <v>105009</v>
+        <v>5169</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6663,34 +6663,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674152</v>
+        <v>674162</v>
       </c>
       <c r="R59" t="n">
-        <v>6607643</v>
+        <v>6607842</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6749,10 +6754,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119715944</v>
+        <v>119717901</v>
       </c>
       <c r="B60" t="n">
-        <v>105009</v>
+        <v>57326</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6761,38 +6766,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674171</v>
+        <v>674244</v>
       </c>
       <c r="R60" t="n">
-        <v>6607629</v>
+        <v>6607812</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6851,10 +6861,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119717901</v>
+        <v>119716052</v>
       </c>
       <c r="B61" t="n">
-        <v>57326</v>
+        <v>105009</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6863,43 +6873,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674244</v>
+        <v>674152</v>
       </c>
       <c r="R61" t="n">
-        <v>6607812</v>
+        <v>6607643</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6958,10 +6963,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119717648</v>
+        <v>119715944</v>
       </c>
       <c r="B62" t="n">
-        <v>5169</v>
+        <v>105009</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6974,39 +6979,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674162</v>
+        <v>674171</v>
       </c>
       <c r="R62" t="n">
-        <v>6607842</v>
+        <v>6607629</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119717226</v>
+        <v>119717901</v>
       </c>
       <c r="B38" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,27 +4463,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674169</v>
+        <v>674244</v>
       </c>
       <c r="R38" t="n">
-        <v>6607879</v>
+        <v>6607812</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4554,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119716838</v>
+        <v>119716909</v>
       </c>
       <c r="B39" t="n">
-        <v>100171</v>
+        <v>105009</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674257</v>
+        <v>674221</v>
       </c>
       <c r="R39" t="n">
-        <v>6607850</v>
+        <v>6607862</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,10 +4656,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119717195</v>
+        <v>119716973</v>
       </c>
       <c r="B40" t="n">
-        <v>74577</v>
+        <v>57326</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,35 +4668,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674160</v>
+        <v>674194</v>
       </c>
       <c r="R40" t="n">
         <v>6607881</v>
@@ -4758,10 +4763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119715881</v>
+        <v>119717027</v>
       </c>
       <c r="B41" t="n">
-        <v>57463</v>
+        <v>105009</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4770,25 +4775,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4798,13 +4803,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674166</v>
+        <v>674194</v>
       </c>
       <c r="R41" t="n">
-        <v>6607637</v>
+        <v>6607917</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4860,7 +4865,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119716495</v>
+        <v>119718472</v>
       </c>
       <c r="B42" t="n">
         <v>105009</v>
@@ -4900,10 +4905,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674218</v>
+        <v>674198</v>
       </c>
       <c r="R42" t="n">
-        <v>6607746</v>
+        <v>6607655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4962,10 +4967,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119717672</v>
+        <v>119714171</v>
       </c>
       <c r="B43" t="n">
-        <v>91182</v>
+        <v>100171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4978,34 +4983,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674166</v>
+        <v>674356</v>
       </c>
       <c r="R43" t="n">
-        <v>6607847</v>
+        <v>6607520</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5064,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119719393</v>
+        <v>119714906</v>
       </c>
       <c r="B44" t="n">
-        <v>57326</v>
+        <v>95455</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,39 +5085,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674375</v>
+        <v>674311</v>
       </c>
       <c r="R44" t="n">
-        <v>6607681</v>
+        <v>6607664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119716905</v>
+        <v>119717489</v>
       </c>
       <c r="B45" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5183,43 +5183,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674225</v>
+        <v>674162</v>
       </c>
       <c r="R45" t="n">
-        <v>6607864</v>
+        <v>6607837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5278,10 +5273,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119717489</v>
+        <v>119716495</v>
       </c>
       <c r="B46" t="n">
-        <v>100171</v>
+        <v>105009</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5294,21 +5289,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5318,10 +5313,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674162</v>
+        <v>674218</v>
       </c>
       <c r="R46" t="n">
-        <v>6607837</v>
+        <v>6607746</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5380,10 +5375,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119719729</v>
+        <v>119717414</v>
       </c>
       <c r="B47" t="n">
-        <v>100171</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5392,38 +5387,52 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674432</v>
+        <v>674201</v>
       </c>
       <c r="R47" t="n">
-        <v>6607590</v>
+        <v>6607851</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5456,6 +5465,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5482,10 +5496,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119717604</v>
+        <v>119716052</v>
       </c>
       <c r="B48" t="n">
-        <v>100171</v>
+        <v>105009</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5498,21 +5512,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5522,10 +5536,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674141</v>
+        <v>674152</v>
       </c>
       <c r="R48" t="n">
-        <v>6607853</v>
+        <v>6607643</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5584,10 +5598,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119716973</v>
+        <v>119719729</v>
       </c>
       <c r="B49" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5596,43 +5610,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674194</v>
+        <v>674432</v>
       </c>
       <c r="R49" t="n">
-        <v>6607881</v>
+        <v>6607590</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5691,10 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119718022</v>
+        <v>119717688</v>
       </c>
       <c r="B50" t="n">
-        <v>104994</v>
+        <v>100171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5707,48 +5716,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674216</v>
+        <v>674174</v>
       </c>
       <c r="R50" t="n">
-        <v>6607800</v>
+        <v>6607837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5807,10 +5802,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119718472</v>
+        <v>119719393</v>
       </c>
       <c r="B51" t="n">
-        <v>105009</v>
+        <v>57326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,38 +5814,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674198</v>
+        <v>674375</v>
       </c>
       <c r="R51" t="n">
-        <v>6607655</v>
+        <v>6607681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717027</v>
+        <v>119717226</v>
       </c>
       <c r="B52" t="n">
-        <v>105009</v>
+        <v>57463</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5921,41 +5921,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674194</v>
+        <v>674169</v>
       </c>
       <c r="R52" t="n">
-        <v>6607917</v>
+        <v>6607879</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6011,10 +6016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119717414</v>
+        <v>119718022</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>104994</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6023,35 +6028,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6065,10 +6070,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674201</v>
+        <v>674216</v>
       </c>
       <c r="R53" t="n">
-        <v>6607851</v>
+        <v>6607800</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6101,11 +6106,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119718457</v>
+        <v>119715944</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>105009</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6144,38 +6144,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674202</v>
+        <v>674171</v>
       </c>
       <c r="R54" t="n">
-        <v>6607652</v>
+        <v>6607629</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119714171</v>
+        <v>119715881</v>
       </c>
       <c r="B55" t="n">
-        <v>100171</v>
+        <v>57463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6246,41 +6246,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674356</v>
+        <v>674166</v>
       </c>
       <c r="R55" t="n">
-        <v>6607520</v>
+        <v>6607637</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119717688</v>
+        <v>119717195</v>
       </c>
       <c r="B56" t="n">
-        <v>100171</v>
+        <v>74577</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674174</v>
+        <v>674160</v>
       </c>
       <c r="R56" t="n">
-        <v>6607837</v>
+        <v>6607881</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119718622</v>
+        <v>119716905</v>
       </c>
       <c r="B57" t="n">
-        <v>105009</v>
+        <v>57326</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6450,38 +6450,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674249</v>
+        <v>674225</v>
       </c>
       <c r="R57" t="n">
-        <v>6607621</v>
+        <v>6607864</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6540,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119719516</v>
+        <v>119716838</v>
       </c>
       <c r="B58" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6552,43 +6557,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674419</v>
+        <v>674257</v>
       </c>
       <c r="R58" t="n">
-        <v>6607656</v>
+        <v>6607850</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6647,10 +6647,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119717648</v>
+        <v>119719516</v>
       </c>
       <c r="B59" t="n">
-        <v>5169</v>
+        <v>57326</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6659,43 +6659,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674162</v>
+        <v>674419</v>
       </c>
       <c r="R59" t="n">
-        <v>6607842</v>
+        <v>6607656</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6754,10 +6754,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119717901</v>
+        <v>119718457</v>
       </c>
       <c r="B60" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6770,39 +6770,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674244</v>
+        <v>674202</v>
       </c>
       <c r="R60" t="n">
-        <v>6607812</v>
+        <v>6607652</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6861,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119716052</v>
+        <v>119717604</v>
       </c>
       <c r="B61" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6877,21 +6872,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6901,10 +6896,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674152</v>
+        <v>674141</v>
       </c>
       <c r="R61" t="n">
-        <v>6607643</v>
+        <v>6607853</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6963,10 +6958,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119715944</v>
+        <v>119717648</v>
       </c>
       <c r="B62" t="n">
-        <v>105009</v>
+        <v>5169</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6979,34 +6974,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674171</v>
+        <v>674162</v>
       </c>
       <c r="R62" t="n">
-        <v>6607629</v>
+        <v>6607842</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7065,10 +7065,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119714906</v>
+        <v>119718622</v>
       </c>
       <c r="B63" t="n">
-        <v>95455</v>
+        <v>105009</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7077,38 +7077,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674311</v>
+        <v>674249</v>
       </c>
       <c r="R63" t="n">
-        <v>6607664</v>
+        <v>6607621</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7274,10 +7274,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119716909</v>
+        <v>119717672</v>
       </c>
       <c r="B65" t="n">
-        <v>105009</v>
+        <v>91182</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7290,21 +7290,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674221</v>
+        <v>674166</v>
       </c>
       <c r="R65" t="n">
-        <v>6607862</v>
+        <v>6607847</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -5700,10 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119717688</v>
+        <v>119719393</v>
       </c>
       <c r="B50" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5712,38 +5712,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674174</v>
+        <v>674375</v>
       </c>
       <c r="R50" t="n">
-        <v>6607837</v>
+        <v>6607681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5802,10 +5807,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119719393</v>
+        <v>119718022</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
+        <v>104994</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5814,43 +5819,52 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674375</v>
+        <v>674216</v>
       </c>
       <c r="R51" t="n">
-        <v>6607681</v>
+        <v>6607800</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5909,10 +5923,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717226</v>
+        <v>119717688</v>
       </c>
       <c r="B52" t="n">
-        <v>57463</v>
+        <v>100171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5921,46 +5935,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674169</v>
+        <v>674174</v>
       </c>
       <c r="R52" t="n">
-        <v>6607879</v>
+        <v>6607837</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6016,10 +6025,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119718022</v>
+        <v>119717226</v>
       </c>
       <c r="B53" t="n">
-        <v>104994</v>
+        <v>57463</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6028,40 +6037,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674216</v>
+        <v>674169</v>
       </c>
       <c r="R53" t="n">
-        <v>6607800</v>
+        <v>6607879</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7167,10 +7167,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119716230</v>
+        <v>119717672</v>
       </c>
       <c r="B64" t="n">
-        <v>8421</v>
+        <v>91182</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7183,39 +7183,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674120</v>
+        <v>674166</v>
       </c>
       <c r="R64" t="n">
-        <v>6607622</v>
+        <v>6607847</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7274,10 +7269,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119717672</v>
+        <v>119716230</v>
       </c>
       <c r="B65" t="n">
-        <v>91182</v>
+        <v>8421</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7290,34 +7285,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674166</v>
+        <v>674120</v>
       </c>
       <c r="R65" t="n">
-        <v>6607847</v>
+        <v>6607622</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -5700,10 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119719393</v>
+        <v>119717688</v>
       </c>
       <c r="B50" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5712,43 +5712,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674375</v>
+        <v>674174</v>
       </c>
       <c r="R50" t="n">
-        <v>6607681</v>
+        <v>6607837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5807,10 +5802,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119718022</v>
+        <v>119719393</v>
       </c>
       <c r="B51" t="n">
-        <v>104994</v>
+        <v>57326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,52 +5814,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674216</v>
+        <v>674375</v>
       </c>
       <c r="R51" t="n">
-        <v>6607800</v>
+        <v>6607681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5923,10 +5909,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717688</v>
+        <v>119717226</v>
       </c>
       <c r="B52" t="n">
-        <v>100171</v>
+        <v>57463</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5935,41 +5921,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674174</v>
+        <v>674169</v>
       </c>
       <c r="R52" t="n">
-        <v>6607837</v>
+        <v>6607879</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6025,10 +6016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119717226</v>
+        <v>119718022</v>
       </c>
       <c r="B53" t="n">
-        <v>57463</v>
+        <v>104994</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6037,31 +6028,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674169</v>
+        <v>674216</v>
       </c>
       <c r="R53" t="n">
-        <v>6607879</v>
+        <v>6607800</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7167,10 +7167,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119717672</v>
+        <v>119716230</v>
       </c>
       <c r="B64" t="n">
-        <v>91182</v>
+        <v>8421</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7183,34 +7183,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674166</v>
+        <v>674120</v>
       </c>
       <c r="R64" t="n">
-        <v>6607847</v>
+        <v>6607622</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7269,10 +7274,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119716230</v>
+        <v>119717672</v>
       </c>
       <c r="B65" t="n">
-        <v>8421</v>
+        <v>91182</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7285,39 +7290,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674120</v>
+        <v>674166</v>
       </c>
       <c r="R65" t="n">
-        <v>6607622</v>
+        <v>6607847</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -5700,10 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119717688</v>
+        <v>119719393</v>
       </c>
       <c r="B50" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5712,38 +5712,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674174</v>
+        <v>674375</v>
       </c>
       <c r="R50" t="n">
-        <v>6607837</v>
+        <v>6607681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5802,10 +5807,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119719393</v>
+        <v>119718022</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
+        <v>104994</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5814,43 +5819,52 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674375</v>
+        <v>674216</v>
       </c>
       <c r="R51" t="n">
-        <v>6607681</v>
+        <v>6607800</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5909,10 +5923,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717226</v>
+        <v>119717688</v>
       </c>
       <c r="B52" t="n">
-        <v>57463</v>
+        <v>100171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5921,46 +5935,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674169</v>
+        <v>674174</v>
       </c>
       <c r="R52" t="n">
-        <v>6607879</v>
+        <v>6607837</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6016,10 +6025,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119718022</v>
+        <v>119717226</v>
       </c>
       <c r="B53" t="n">
-        <v>104994</v>
+        <v>57463</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6028,40 +6037,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674216</v>
+        <v>674169</v>
       </c>
       <c r="R53" t="n">
-        <v>6607800</v>
+        <v>6607879</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -5700,10 +5700,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119719393</v>
+        <v>119717688</v>
       </c>
       <c r="B50" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5712,43 +5712,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674375</v>
+        <v>674174</v>
       </c>
       <c r="R50" t="n">
-        <v>6607681</v>
+        <v>6607837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5807,10 +5802,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119718022</v>
+        <v>119719393</v>
       </c>
       <c r="B51" t="n">
-        <v>104994</v>
+        <v>57326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,52 +5814,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674216</v>
+        <v>674375</v>
       </c>
       <c r="R51" t="n">
-        <v>6607800</v>
+        <v>6607681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5923,10 +5909,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717688</v>
+        <v>119717226</v>
       </c>
       <c r="B52" t="n">
-        <v>100171</v>
+        <v>57463</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5935,41 +5921,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674174</v>
+        <v>674169</v>
       </c>
       <c r="R52" t="n">
-        <v>6607837</v>
+        <v>6607879</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6025,10 +6016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119717226</v>
+        <v>119718022</v>
       </c>
       <c r="B53" t="n">
-        <v>57463</v>
+        <v>104994</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6037,31 +6028,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674169</v>
+        <v>674216</v>
       </c>
       <c r="R53" t="n">
-        <v>6607879</v>
+        <v>6607800</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>

--- a/artfynd/A 42742-2023 artfynd.xlsx
+++ b/artfynd/A 42742-2023 artfynd.xlsx
@@ -4447,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119717901</v>
+        <v>119715944</v>
       </c>
       <c r="B38" t="n">
-        <v>57326</v>
+        <v>105032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4459,43 +4459,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674244</v>
+        <v>674171</v>
       </c>
       <c r="R38" t="n">
-        <v>6607812</v>
+        <v>6607629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4554,10 +4549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119716909</v>
+        <v>119718457</v>
       </c>
       <c r="B39" t="n">
-        <v>105009</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4566,38 +4561,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674221</v>
+        <v>674202</v>
       </c>
       <c r="R39" t="n">
-        <v>6607862</v>
+        <v>6607652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,10 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119716973</v>
+        <v>119715881</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>57473</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4672,42 +4667,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674194</v>
+        <v>674166</v>
       </c>
       <c r="R40" t="n">
-        <v>6607881</v>
+        <v>6607637</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4763,10 +4753,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119717027</v>
+        <v>119716909</v>
       </c>
       <c r="B41" t="n">
-        <v>105009</v>
+        <v>105032</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4803,10 +4793,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674194</v>
+        <v>674221</v>
       </c>
       <c r="R41" t="n">
-        <v>6607917</v>
+        <v>6607862</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4865,10 +4855,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119718472</v>
+        <v>119717688</v>
       </c>
       <c r="B42" t="n">
-        <v>105009</v>
+        <v>100194</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,21 +4871,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4905,10 +4895,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674198</v>
+        <v>674174</v>
       </c>
       <c r="R42" t="n">
-        <v>6607655</v>
+        <v>6607837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4967,10 +4957,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119714171</v>
+        <v>119718472</v>
       </c>
       <c r="B43" t="n">
-        <v>100171</v>
+        <v>105032</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4983,34 +4973,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674356</v>
+        <v>674198</v>
       </c>
       <c r="R43" t="n">
-        <v>6607520</v>
+        <v>6607655</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5069,10 +5059,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119714906</v>
+        <v>119717414</v>
       </c>
       <c r="B44" t="n">
-        <v>95455</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5081,38 +5071,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674311</v>
+        <v>674201</v>
       </c>
       <c r="R44" t="n">
-        <v>6607664</v>
+        <v>6607851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5145,6 +5149,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,10 +5180,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119717489</v>
+        <v>119717027</v>
       </c>
       <c r="B45" t="n">
-        <v>100171</v>
+        <v>105032</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,21 +5196,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5211,10 +5220,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674162</v>
+        <v>674194</v>
       </c>
       <c r="R45" t="n">
-        <v>6607837</v>
+        <v>6607917</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5273,10 +5282,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119716495</v>
+        <v>119717226</v>
       </c>
       <c r="B46" t="n">
-        <v>105009</v>
+        <v>57473</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5285,41 +5294,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674218</v>
+        <v>674169</v>
       </c>
       <c r="R46" t="n">
-        <v>6607746</v>
+        <v>6607879</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5375,10 +5389,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119717414</v>
+        <v>119717489</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>100194</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5387,52 +5401,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674201</v>
+        <v>674162</v>
       </c>
       <c r="R47" t="n">
-        <v>6607851</v>
+        <v>6607837</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5465,11 +5465,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld. Förröjning inför avverkning har skett.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5496,10 +5491,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119716052</v>
+        <v>119716973</v>
       </c>
       <c r="B48" t="n">
-        <v>105009</v>
+        <v>57336</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,38 +5503,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674152</v>
+        <v>674194</v>
       </c>
       <c r="R48" t="n">
-        <v>6607643</v>
+        <v>6607881</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119719729</v>
+        <v>119719516</v>
       </c>
       <c r="B49" t="n">
-        <v>100171</v>
+        <v>57336</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5610,38 +5610,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674432</v>
+        <v>674419</v>
       </c>
       <c r="R49" t="n">
-        <v>6607590</v>
+        <v>6607656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5700,10 +5705,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119719393</v>
+        <v>119718022</v>
       </c>
       <c r="B50" t="n">
-        <v>57326</v>
+        <v>105017</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5712,43 +5717,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674375</v>
+        <v>674216</v>
       </c>
       <c r="R50" t="n">
-        <v>6607681</v>
+        <v>6607800</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5807,10 +5821,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119718022</v>
+        <v>119716905</v>
       </c>
       <c r="B51" t="n">
-        <v>104994</v>
+        <v>57336</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,40 +5833,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5861,10 +5866,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674216</v>
+        <v>674225</v>
       </c>
       <c r="R51" t="n">
-        <v>6607800</v>
+        <v>6607864</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5923,10 +5928,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119717688</v>
+        <v>119716052</v>
       </c>
       <c r="B52" t="n">
-        <v>100171</v>
+        <v>105032</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5939,21 +5944,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5963,10 +5968,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674174</v>
+        <v>674152</v>
       </c>
       <c r="R52" t="n">
-        <v>6607837</v>
+        <v>6607643</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6025,10 +6030,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119717226</v>
+        <v>119716838</v>
       </c>
       <c r="B53" t="n">
-        <v>57463</v>
+        <v>100194</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6037,46 +6042,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674169</v>
+        <v>674257</v>
       </c>
       <c r="R53" t="n">
-        <v>6607879</v>
+        <v>6607850</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119715944</v>
+        <v>119717672</v>
       </c>
       <c r="B54" t="n">
-        <v>105009</v>
+        <v>91200</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674171</v>
+        <v>674166</v>
       </c>
       <c r="R54" t="n">
-        <v>6607629</v>
+        <v>6607847</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119715881</v>
+        <v>119718622</v>
       </c>
       <c r="B55" t="n">
-        <v>57463</v>
+        <v>105032</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6246,41 +6246,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674166</v>
+        <v>674249</v>
       </c>
       <c r="R55" t="n">
-        <v>6607637</v>
+        <v>6607621</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119717195</v>
+        <v>119719393</v>
       </c>
       <c r="B56" t="n">
-        <v>74577</v>
+        <v>57336</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6348,38 +6348,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Hökboberget, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674160</v>
+        <v>674375</v>
       </c>
       <c r="R56" t="n">
-        <v>6607881</v>
+        <v>6607681</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6438,10 +6443,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119716905</v>
+        <v>119719729</v>
       </c>
       <c r="B57" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6450,43 +6455,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674225</v>
+        <v>674432</v>
       </c>
       <c r="R57" t="n">
-        <v>6607864</v>
+        <v>6607590</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6545,10 +6545,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119716838</v>
+        <v>119717195</v>
       </c>
       <c r="B58" t="n">
-        <v>100171</v>
+        <v>74593</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6561,21 +6561,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674257</v>
+        <v>674160</v>
       </c>
       <c r="R58" t="n">
-        <v>6607850</v>
+        <v>6607881</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6647,10 +6647,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119719516</v>
+        <v>119717901</v>
       </c>
       <c r="B59" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6688,14 +6688,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674419</v>
+        <v>674244</v>
       </c>
       <c r="R59" t="n">
-        <v>6607656</v>
+        <v>6607812</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6754,10 +6754,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119718457</v>
+        <v>119717648</v>
       </c>
       <c r="B60" t="n">
-        <v>90562</v>
+        <v>5169</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6766,38 +6766,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674202</v>
+        <v>674162</v>
       </c>
       <c r="R60" t="n">
-        <v>6607652</v>
+        <v>6607842</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,10 +6861,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119717604</v>
+        <v>119714906</v>
       </c>
       <c r="B61" t="n">
-        <v>100171</v>
+        <v>95478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6868,38 +6873,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674141</v>
+        <v>674311</v>
       </c>
       <c r="R61" t="n">
-        <v>6607853</v>
+        <v>6607664</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6958,10 +6963,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119717648</v>
+        <v>119714171</v>
       </c>
       <c r="B62" t="n">
-        <v>5169</v>
+        <v>100194</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6974,39 +6979,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hökboberget, Hökboberget, Upl</t>
+          <t>Dalen, Dalen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674162</v>
+        <v>674356</v>
       </c>
       <c r="R62" t="n">
-        <v>6607842</v>
+        <v>6607520</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7065,10 +7065,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119718622</v>
+        <v>119717604</v>
       </c>
       <c r="B63" t="n">
-        <v>105009</v>
+        <v>100194</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7081,34 +7081,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hökboberget, Dalen, Upl</t>
+          <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674249</v>
+        <v>674141</v>
       </c>
       <c r="R63" t="n">
-        <v>6607621</v>
+        <v>6607853</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7167,10 +7167,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119716230</v>
+        <v>119716495</v>
       </c>
       <c r="B64" t="n">
-        <v>8421</v>
+        <v>105032</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7183,39 +7183,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674120</v>
+        <v>674218</v>
       </c>
       <c r="R64" t="n">
-        <v>6607622</v>
+        <v>6607746</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7274,10 +7269,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119717672</v>
+        <v>119716230</v>
       </c>
       <c r="B65" t="n">
-        <v>91182</v>
+        <v>8421</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7290,34 +7285,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hökboberget, Hökboberget, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674166</v>
+        <v>674120</v>
       </c>
       <c r="R65" t="n">
-        <v>6607847</v>
+        <v>6607622</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
